--- a/saved_reports.xlsx
+++ b/saved_reports.xlsx
@@ -506,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26092401</t>
+          <t>26092601</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:16</t>
+          <t>2026-09-26 12:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Not sure / I don't know</t>
+          <t>Type 1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -572,7 +572,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+          <t>The patient denies any of the core symptoms assessed in this screening. On further questioning, the patient also endorses Blurry or unclear vision.</t>
         </is>
       </c>
     </row>

--- a/saved_reports.xlsx
+++ b/saved_reports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,12 +502,20 @@
           <t>Symptom narrative</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Type-specific answers</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>26092601</t>
-        </is>
+      <c r="A2" t="n">
+        <v>26092601</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -524,10 +532,8 @@
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0771715275</t>
-        </is>
+      <c r="E2" t="n">
+        <v>771715275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -573,6 +579,470 @@
       <c r="Q2" t="inlineStr">
         <is>
           <t>The patient denies any of the core symptoms assessed in this screening. On further questioning, the patient also endorses Blurry or unclear vision.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>26092901</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:34</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PP-000001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP-000001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>24</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+256771715275</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
     </row>

--- a/saved_reports.xlsx
+++ b/saved_reports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,31 @@
           <t>Type-specific answers</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Assessment ID</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Model version</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Probability method</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Decision threshold</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Clinical interpretation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -583,6 +608,11 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -658,6 +688,11 @@
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -735,6 +770,11 @@
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -812,6 +852,11 @@
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -889,6 +934,11 @@
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -966,6 +1016,11 @@
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -988,10 +1043,8 @@
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+256771715275</t>
-        </is>
+      <c r="E8" t="n">
+        <v>256771715275</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1043,6 +1096,301 @@
       <c r="S8" t="inlineStr">
         <is>
           <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:41:25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>23.0%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>The patient reports Alopecia (abnormal hair loss).</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ae5108bb91d058d2fe7239063420ec89</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:36:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>a1c62cfc176fa031d2a5457e504c0b44</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PP-grouped-2026-09-30-v1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>forest / tested pipeline predict_proba</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>26092901</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:50:51</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+256771715275</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>The patient denies all core and additional symptoms assessed in this screening.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Has a doctor prescribed insulin for you?: No; Have you had episodes of low blood sugar?: No; Have you ever been told your ketones were high?: No</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>766f5fc534350a0a1c863bd04a6841dc</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>PP-grouped-2026-09-30-v1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>forest / tested pipeline predict_proba</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
         </is>
       </c>
     </row>

--- a/saved_reports.xlsx
+++ b/saved_reports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,11 @@
       <c r="X1" t="inlineStr">
         <is>
           <t>Clinical interpretation</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Patient notes</t>
         </is>
       </c>
     </row>
@@ -613,6 +618,7 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -693,6 +699,7 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -775,6 +782,7 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -857,6 +865,7 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +948,7 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1021,6 +1031,7 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1103,6 +1114,7 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1189,6 +1201,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1289,6 +1302,7 @@
           <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1311,10 +1325,8 @@
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>+256771715275</t>
-        </is>
+      <c r="E11" t="n">
+        <v>256771715275</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -1383,16 +1395,322 @@
           <t>forest / tested pipeline predict_proba</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>26100101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-01 03:54:08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Not sure / I don't know</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>19.1%</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Reduced sex drive</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>The patient reports Itching. On further questioning, the patient also endorses Do you take any medicines regularly? and Reduced sex drive.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>d2852ac91ecace2b5fa712a2b4e4c1c6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PP-grouped-2026-09-30-v1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>forest / tested pipeline predict_proba</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>26100101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-01 03:54:09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>256771715275</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Not sure / I don't know</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Negative (low risk)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>19.1%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Reduced sex drive</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>The patient reports Itching. On further questioning, the patient also endorses Do you take any medicines regularly? and Reduced sex drive.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4b8aba9e3ef2ba90ed29616af730199c</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PP-grouped-2026-09-30-v1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>forest / tested pipeline predict_proba</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>26100101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-01 04:11:07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+256771715275</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Not sure / I don't know</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Single (never married)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Positive (high risk)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>88.7%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8-10 times a day</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The patient reports Polyuria (excessive urination) (8-10 times a day) and Itching. On further questioning, the patient also endorses Do you often have trouble sleeping?.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6864548375e6558a3cbebfe59c4da41e</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PP-grouped-2026-09-30-v1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>forest / tested pipeline predict_proba</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Educational screening estimate; not a diagnosis or an externally validated individual risk.</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
